--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484370_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484370_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.56</v>
+        <v>4.3099</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4031</v>
+        <v>1.3513</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1569</v>
+        <v>2.9586</v>
       </c>
       <c r="G2" t="n">
         <v>2.3274</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3196</v>
+        <v>1.0695</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8945</v>
+        <v>-0.1573</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4251</v>
+        <v>1.2267</v>
       </c>
       <c r="V2" t="n">
         <v>1.1083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2699</v>
+        <v>2.089</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.2351</v>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>2.3241</v>
       </c>
       <c r="G3" t="n">
         <v>2.91</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4945</v>
+        <v>-0.6755</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1278</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3667</v>
+        <v>-0.0126</v>
       </c>
       <c r="V3" t="n">
         <v>0.8310999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4009</v>
+        <v>0.1521</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.5046</v>
+        <v>-2.8079</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9055</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6057</v>
@@ -766,13 +766,13 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0968</v>
+        <v>-0.152</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0167</v>
+        <v>-0.2866</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0801</v>
+        <v>0.1346</v>
       </c>
       <c r="V4" t="n">
         <v>1.4959</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. SANCHO GERVÁS</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5384</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0701</v>
+        <v>-0.7267</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6085</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0129</v>
+        <v>4.0117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0663</v>
+        <v>3.7824</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0792</v>
+        <v>0.2294</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0013</v>
+        <v>2.8884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0013</v>
+        <v>2.9279</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.0395</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0142</v>
+        <v>1.1233</v>
       </c>
       <c r="N5" t="n">
-        <v>0.065</v>
+        <v>0.8545</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0792</v>
+        <v>0.2688</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9471000000000001</v>
+        <v>-0.7484</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0456</v>
+        <v>-0.6849</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0985</v>
+        <v>-0.0634</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.749</v>
+        <v>-0.8367</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1312</v>
+        <v>-0.8518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3822</v>
+        <v>0.0151</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0117</v>
+        <v>-2.0576</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7824</v>
+        <v>-1.1942</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2294</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8884</v>
+        <v>-0.5637</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9279</v>
+        <v>-1.1845</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0395</v>
+        <v>0.6208</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1233</v>
+        <v>-1.4939</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8545</v>
+        <v>-0.0097</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2688</v>
+        <v>-1.4842</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5886</v>
+        <v>-0.0873</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0894</v>
+        <v>-0.2881</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4992</v>
+        <v>0.2008</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>0.3315</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0.3315</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0505</v>
+        <v>-0.9028</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4698</v>
+        <v>-3.2676</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4193</v>
+        <v>2.3648</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3126</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.738</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1094</v>
+        <v>0.0549</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3095</v>
+        <v>-1.0262</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2156</v>
+        <v>-1.6134</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0939</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0576</v>
+        <v>-1.083</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1942</v>
+        <v>0.0506</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-1.1336</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5637</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1845</v>
+        <v>0.6792</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6208</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4939</v>
+        <v>-1.169</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0097</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4842</v>
+        <v>-0.5405</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5601</v>
+        <v>0.1438</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.652</v>
+        <v>-0.3004</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.4442</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3315</v>
+        <v>0.499</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3315</v>
+        <v>-0.0554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>F. SANCHO GERVÁS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4874</v>
+        <v>-1.2928</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.775</v>
+        <v>-0.7388</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2876</v>
+        <v>-0.5541</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.083</v>
+        <v>-1.0129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0506</v>
+        <v>0.0663</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1336</v>
+        <v>-1.0792</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0013</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6792</v>
+        <v>0.0013</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.169</v>
+        <v>-1.0142</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5405</v>
+        <v>-1.0792</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3174</v>
+        <v>0.1926</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4621</v>
+        <v>0.2367</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1446</v>
+        <v>-0.044</v>
       </c>
       <c r="V9" t="n">
-        <v>0.499</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0554</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7277</v>
+        <v>-1.3656</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4484</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2793</v>
+        <v>-1.4468</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2672</v>
+        <v>-2.5174</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8499</v>
+        <v>-0.5344</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.117</v>
+        <v>-1.983</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2668</v>
+        <v>-1.2835</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0409</v>
+        <v>0.0243</v>
       </c>
       <c r="L10" t="n">
         <v>-1.3077</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0004</v>
+        <v>-1.234</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8089</v>
+        <v>-0.5587</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8093</v>
+        <v>-0.6753</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3786</v>
+        <v>0.172</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1816</v>
+        <v>-0.4084</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.197</v>
+        <v>0.5804</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>-0.3875</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-2.1606</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8694</v>
+        <v>-1.4165</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.586</v>
+        <v>-1.2461</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2834</v>
+        <v>-0.1704</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5174</v>
+        <v>-1.2672</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5344</v>
+        <v>0.8499</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.983</v>
+        <v>-2.117</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2835</v>
+        <v>-1.2668</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0243</v>
+        <v>0.0409</v>
       </c>
       <c r="L11" t="n">
         <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.234</v>
+        <v>-0.0004</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5587</v>
+        <v>0.8089</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6753</v>
+        <v>-0.8093</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3318</v>
+        <v>-0.0674</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0756</v>
+        <v>0.0207</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7438</v>
+        <v>-0.0881</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3875</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1606</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
@@ -1345,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5011000000000008</v>
+        <v>-0.1983000000000008</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.3575</v>
+        <v>-10.0549</v>
       </c>
       <c r="F12" t="n">
-        <v>9.856400000000001</v>
+        <v>9.8565</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3927000000000009</v>
+        <v>0.3927000000000007</v>
       </c>
       <c r="H12" t="n">
         <v>8.4871</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.094099999999999</v>
+        <v>-8.094100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>0.9217</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6356</v>
+        <v>5.635599999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.713800000000001</v>
+        <v>-4.7138</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5290999999999999</v>
+        <v>-0.5291000000000006</v>
       </c>
       <c r="N12" t="n">
         <v>2.8514</v>
@@ -1390,13 +1390,13 @@
         <v>11.7205</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0455</v>
+        <v>-0.7429</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.479</v>
+        <v>-3.1762</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4334</v>
+        <v>2.4335</v>
       </c>
       <c r="V12" t="n">
         <v>2.1053</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7833</v>
+        <v>3.0949</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8696</v>
+        <v>1.2629</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9137</v>
+        <v>1.832</v>
       </c>
       <c r="G13" t="n">
         <v>1.6562</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4753</v>
+        <v>0.7869</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6908</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7845</v>
+        <v>0.7028</v>
       </c>
       <c r="V13" t="n">
         <v>0.0658</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9624</v>
+        <v>1.755</v>
       </c>
       <c r="E14" t="n">
-        <v>0.733</v>
+        <v>0.2274</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2293</v>
+        <v>1.5276</v>
       </c>
       <c r="G14" t="n">
         <v>0.6326000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2246</v>
+        <v>0.0172</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2588</v>
+        <v>-0.2468</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0342</v>
+        <v>0.264</v>
       </c>
       <c r="V14" t="n">
         <v>1.4959</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2952</v>
+        <v>0.8759</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2417</v>
+        <v>-2.3057</v>
       </c>
       <c r="F15" t="n">
-        <v>1.537</v>
+        <v>3.1816</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3163</v>
+        <v>0.2428</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0747</v>
+        <v>-1.483</v>
       </c>
       <c r="I15" t="n">
-        <v>0.391</v>
+        <v>1.7258</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1214</v>
+        <v>-0.5413</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-1.3239</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>0.7827</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1949</v>
+        <v>0.7841</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0747</v>
+        <v>-0.1591</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2696</v>
+        <v>0.9431</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7054</v>
+        <v>0.2277</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6136</v>
+        <v>-0.4008</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>-0.376</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8853</v>
+        <v>0.7274</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1628</v>
+        <v>-0.6462</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0481</v>
+        <v>1.3736</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6974</v>
+        <v>0.3163</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1822</v>
+        <v>-0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4848</v>
+        <v>0.391</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3927</v>
+        <v>0.1214</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6089</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2161</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3046</v>
+        <v>0.1949</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5733</v>
+        <v>-0.0747</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2687</v>
+        <v>0.2696</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0089</v>
+        <v>0.1375</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2066</v>
+        <v>0.2091</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8023</v>
+        <v>-0.0716</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2077</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2077</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5074</v>
+        <v>-0.1469</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.418</v>
+        <v>-1.5673</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9106</v>
+        <v>1.4204</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2428</v>
+        <v>-0.6974</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.483</v>
+        <v>-1.1822</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7258</v>
+        <v>0.4848</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5413</v>
+        <v>-0.3927</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3239</v>
+        <v>-0.6089</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7827</v>
+        <v>0.2161</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7841</v>
+        <v>-0.3046</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1591</v>
+        <v>-0.5733</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9431</v>
+        <v>0.2687</v>
       </c>
       <c r="P17" t="n">
         <v>0.7814</v>
@@ -1780,22 +1780,22 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1556</v>
+        <v>0.9767</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5131</v>
+        <v>-0.1978</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3575</v>
+        <v>1.1746</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.376</v>
+        <v>-1.2077</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.011</v>
+        <v>-1.2077</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7085</v>
+        <v>-0.2846</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6931</v>
+        <v>-1.1875</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9846</v>
+        <v>0.9029</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9036999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2774</v>
+        <v>0.1465</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.2207</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4489</v>
+        <v>0.3672</v>
       </c>
       <c r="V18" t="n">
         <v>0.2772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2109</v>
+        <v>-1.0158</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5326</v>
+        <v>-1.722</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6783</v>
+        <v>0.7062</v>
       </c>
       <c r="G19" t="n">
-        <v>0.995</v>
+        <v>-2.1615</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4886</v>
+        <v>-1.2448</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4836</v>
+        <v>-0.9167</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8848</v>
+        <v>-1.8719</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4644</v>
+        <v>-0.5513</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3492</v>
+        <v>-1.3206</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1102</v>
+        <v>-0.2897</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0243</v>
+        <v>-0.6935</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>0.4039</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0127</v>
+        <v>0.1114</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2588</v>
+        <v>-0.092</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2461</v>
+        <v>0.2035</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>1.2296</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1052</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3815</v>
+        <v>-1.181</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9242</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.2439</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1615</v>
+        <v>0.995</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2448</v>
+        <v>-0.4886</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9167</v>
+        <v>1.4836</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8719</v>
+        <v>0.8848</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5513</v>
+        <v>-0.4644</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3206</v>
+        <v>1.3492</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2897</v>
+        <v>0.1102</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6935</v>
+        <v>-0.0243</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4039</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2542</v>
+        <v>0.0427</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2943</v>
+        <v>-0.1457</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0401</v>
+        <v>0.1883</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2296</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0.011</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6501</v>
+        <v>-1.3117</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2549</v>
+        <v>0.4572</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.905</v>
+        <v>-1.7688</v>
       </c>
       <c r="G21" t="n">
         <v>0.9895</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8116</v>
+        <v>-0.4732</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0854</v>
+        <v>0.0508</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8279</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9668</v>
+        <v>-1.338</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7415</v>
+        <v>-3.4381</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7746</v>
+        <v>2.1001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4626</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.2538</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2021</v>
+        <v>-0.8988</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3195</v>
+        <v>0.645</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5983000000000001</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5009999999999994</v>
+        <v>1.175199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.856399999999999</v>
+        <v>-9.856299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>10.3574</v>
+        <v>11.0317</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3927999999999996</v>
@@ -2224,7 +2224,7 @@
         <v>0.5288999999999997</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.8513</v>
+        <v>-2.851300000000001</v>
       </c>
       <c r="L23" t="n">
         <v>3.3803</v>
@@ -2248,13 +2248,13 @@
         <v>13.6739</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0455</v>
+        <v>1.7196</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.4335</v>
+        <v>-2.4334</v>
       </c>
       <c r="U23" t="n">
-        <v>3.4789</v>
+        <v>4.1531</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1051</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484370_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484370_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.0554</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.0554</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1521</v>
+        <v>0.614</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8079</v>
+        <v>0.614</v>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6057</v>
+        <v>0.614</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1758</v>
+        <v>0.614</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7815</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.0637</v>
+        <v>0.614</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6089</v>
+        <v>0.614</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4548</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7846</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6733</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.152</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7267</v>
+        <v>0.307</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0117</v>
+        <v>0.307</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7824</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2294</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8884</v>
+        <v>0.307</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9279</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0395</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1233</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8545</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2688</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7484</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6849</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0634</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8367</v>
+        <v>0.1521</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8518</v>
+        <v>-2.8079</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0151</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0576</v>
+        <v>-0.6057</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1942</v>
+        <v>0.1758</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.7815</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5637</v>
+        <v>-2.0637</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1845</v>
+        <v>-0.6089</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6208</v>
+        <v>-1.4548</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4939</v>
+        <v>1.458</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0097</v>
+        <v>0.7846</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4842</v>
+        <v>0.6733</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0873</v>
+        <v>-0.152</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2881</v>
+        <v>-0.2866</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2008</v>
+        <v>0.1346</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3315</v>
+        <v>1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3315</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9028</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2676</v>
+        <v>-0.7267</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3648</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3126</v>
+        <v>4.0117</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3937</v>
+        <v>3.7824</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.2294</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6458</v>
+        <v>2.8884</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9184</v>
+        <v>2.9279</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7274</v>
+        <v>-0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3332</v>
+        <v>1.1233</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.8545</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8085</v>
+        <v>0.2688</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.7484</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6451</v>
+        <v>-0.6849</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0549</v>
+        <v>-0.0634</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0262</v>
+        <v>-0.8367</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6134</v>
+        <v>-0.8518</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.083</v>
+        <v>-2.0576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0506</v>
+        <v>-1.1942</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1336</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.5637</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6792</v>
+        <v>-1.1845</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.6208</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.169</v>
+        <v>-1.4939</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5405</v>
+        <v>-1.4842</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1438</v>
+        <v>-0.0873</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3004</v>
+        <v>-0.2881</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4442</v>
+        <v>0.2008</v>
       </c>
       <c r="V8" t="n">
-        <v>0.499</v>
+        <v>0.3315</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0554</v>
+        <v>0.3315</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SANCHO GERVÁS</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2928</v>
+        <v>-1.2098</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7388</v>
+        <v>-3.5746</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5541</v>
+        <v>2.3648</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0129</v>
+        <v>-0.6196</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0663</v>
+        <v>-0.7007</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0792</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0013</v>
+        <v>-1.9528</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0013</v>
+        <v>-1.2254</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7274</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0142</v>
+        <v>1.3332</v>
       </c>
       <c r="N9" t="n">
-        <v>0.065</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0792</v>
+        <v>0.8085</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1926</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2367</v>
+        <v>-0.6451</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.044</v>
+        <v>0.0549</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>F. SANCHO GERVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3656</v>
+        <v>-1.2928</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.7388</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4468</v>
+        <v>-0.5541</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5174</v>
+        <v>-1.0129</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5344</v>
+        <v>0.0663</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.983</v>
+        <v>-1.0792</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2835</v>
+        <v>0.0013</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0243</v>
+        <v>0.0013</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.234</v>
+        <v>-1.0142</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5587</v>
+        <v>0.065</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6753</v>
+        <v>-1.0792</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.172</v>
+        <v>0.1926</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4084</v>
+        <v>0.2367</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5804</v>
+        <v>-0.044</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3875</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1606</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4165</v>
+        <v>-1.3656</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2461</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1704</v>
+        <v>-1.4468</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2672</v>
+        <v>-2.5174</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8499</v>
+        <v>-0.5344</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.117</v>
+        <v>-1.983</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2668</v>
+        <v>-1.2835</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0409</v>
+        <v>0.0243</v>
       </c>
       <c r="L11" t="n">
         <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0004</v>
+        <v>-1.234</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8089</v>
+        <v>-0.5587</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8093</v>
+        <v>-0.6753</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0674</v>
+        <v>0.172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0207</v>
+        <v>-0.4084</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0881</v>
+        <v>0.5804</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>-0.3875</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-2.1606</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1983000000000008</v>
+        <v>-1.4165</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.0549</v>
+        <v>-1.2461</v>
       </c>
       <c r="F12" t="n">
-        <v>9.8565</v>
+        <v>-0.1704</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3927000000000007</v>
+        <v>-1.2672</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4871</v>
+        <v>0.8499</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.094100000000001</v>
+        <v>-2.117</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9217</v>
+        <v>-1.2668</v>
       </c>
       <c r="K12" t="n">
-        <v>5.635599999999999</v>
+        <v>0.0409</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.7138</v>
+        <v>-1.3077</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5291000000000006</v>
+        <v>-0.0004</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8514</v>
+        <v>0.8089</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.3805</v>
+        <v>-0.8093</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9533</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6738</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7205</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7429</v>
+        <v>-0.0674</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1762</v>
+        <v>0.0207</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4335</v>
+        <v>-0.0881</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1053</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>5.873799999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7683</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0949</v>
+        <v>-1.6402</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2629</v>
+        <v>-2.2273</v>
       </c>
       <c r="F13" t="n">
-        <v>1.832</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6562</v>
+        <v>-1.697</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8463000000000001</v>
+        <v>-0.5633</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8099</v>
+        <v>-1.1336</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5462</v>
+        <v>-0.528</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6795</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1332</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.11</v>
+        <v>-1.169</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9431</v>
+        <v>-0.5405</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7869</v>
+        <v>0.1438</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.3004</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7028</v>
+        <v>0.4442</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0658</v>
+        <v>0.499</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5435</v>
+        <v>-0.0554</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.755</v>
+        <v>-0.1982999999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2274</v>
+        <v>-10.0548</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5276</v>
+        <v>9.856499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.3926999999999996</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3528</v>
+        <v>8.487200000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9854000000000001</v>
+        <v>-8.094100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9318</v>
+        <v>0.9217</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3505</v>
+        <v>5.635599999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5813</v>
+        <v>-4.713800000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2992</v>
+        <v>-0.5291000000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7032</v>
+        <v>2.8514</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4041</v>
+        <v>-3.3805</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>-1.9533</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-13.6738</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>11.7205</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0172</v>
+        <v>-0.7429000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2468</v>
+        <v>-3.1762</v>
       </c>
       <c r="U14" t="n">
-        <v>0.264</v>
+        <v>2.4335</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4959</v>
+        <v>2.1053</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>5.8738</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.7683</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8759</v>
+        <v>3.0949</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3057</v>
+        <v>1.2629</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1816</v>
+        <v>1.832</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2428</v>
+        <v>1.6562</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.483</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7258</v>
+        <v>0.8099</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5413</v>
+        <v>1.5462</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3239</v>
+        <v>1.6795</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7827</v>
+        <v>-0.1332</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7841</v>
+        <v>0.11</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1591</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>0.9431</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2277</v>
+        <v>0.7869</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4008</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.7028</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.376</v>
+        <v>0.0658</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3869</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>0.011</v>
+        <v>-0.5435</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7274</v>
+        <v>1.141</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6462</v>
+        <v>-0.3865</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3736</v>
+        <v>1.5276</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3163</v>
+        <v>0.0186</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0747</v>
+        <v>-0.9667</v>
       </c>
       <c r="I16" t="n">
-        <v>0.391</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1214</v>
+        <v>0.3178</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.2635</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1214</v>
+        <v>0.5813</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1949</v>
+        <v>-0.2992</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0747</v>
+        <v>-0.7032</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2696</v>
+        <v>0.4041</v>
       </c>
       <c r="P16" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1375</v>
+        <v>0.0172</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2091</v>
+        <v>-0.2468</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0716</v>
+        <v>0.264</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>1.4959</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1811,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1469</v>
+        <v>0.8759</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5673</v>
+        <v>-2.3057</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4204</v>
+        <v>3.1816</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6974</v>
+        <v>0.2428</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1822</v>
+        <v>-1.483</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4848</v>
+        <v>1.7258</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3927</v>
+        <v>-0.5413</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6089</v>
+        <v>-1.3239</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2161</v>
+        <v>0.7827</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3046</v>
+        <v>0.7841</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5733</v>
+        <v>-0.1591</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2687</v>
+        <v>0.9431</v>
       </c>
       <c r="P17" t="n">
         <v>0.7814</v>
@@ -1780,28 +1856,33 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9767</v>
+        <v>0.2277</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1978</v>
+        <v>-0.4008</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1746</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2077</v>
+        <v>-0.376</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2077</v>
+        <v>0.011</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2846</v>
+        <v>0.7274</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1875</v>
+        <v>-0.6462</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9029</v>
+        <v>1.3736</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.3163</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9716</v>
+        <v>-0.0747</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0679</v>
+        <v>0.391</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5446</v>
+        <v>0.1214</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.606</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3591</v>
+        <v>0.1949</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.033</v>
+        <v>-0.0747</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.2696</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1465</v>
+        <v>0.1375</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2207</v>
+        <v>0.2091</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3672</v>
+        <v>-0.0716</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0158</v>
+        <v>0.614</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.722</v>
+        <v>0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7062</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1615</v>
+        <v>0.614</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2448</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9167</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8719</v>
+        <v>0.614</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5513</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3206</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2897</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6935</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4039</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1114</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2035</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2296</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.011</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.181</v>
+        <v>-0.1469</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-1.5673</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2439</v>
+        <v>1.4204</v>
       </c>
       <c r="G20" t="n">
-        <v>0.995</v>
+        <v>-0.6974</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4886</v>
+        <v>-1.1822</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4836</v>
+        <v>0.4848</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8848</v>
+        <v>-0.3927</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4644</v>
+        <v>-0.6089</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3492</v>
+        <v>0.2161</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1102</v>
+        <v>-0.3046</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0243</v>
+        <v>-0.5733</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1344</v>
+        <v>0.2687</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0427</v>
+        <v>0.9767</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1457</v>
+        <v>-0.1978</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1883</v>
+        <v>1.1746</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-1.2077</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1052</v>
+        <v>-1.2077</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3117</v>
+        <v>-0.2846</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4572</v>
+        <v>-1.1875</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7688</v>
+        <v>0.9029</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9895</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2517</v>
+        <v>-0.9716</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2412</v>
+        <v>0.0679</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9579</v>
+        <v>-0.5446</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7163</v>
+        <v>0.0614</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2416</v>
+        <v>-0.606</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9684</v>
+        <v>-0.3591</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.968</v>
+        <v>-1.033</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0004</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4732</v>
+        <v>0.1465</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.524</v>
+        <v>-0.2207</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0508</v>
+        <v>0.3672</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8279</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.338</v>
+        <v>-1.0158</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4381</v>
+        <v>-1.722</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1001</v>
+        <v>0.7062</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4626</v>
+        <v>-2.1615</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2838</v>
+        <v>-1.2448</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8212</v>
+        <v>-0.9167</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5627</v>
+        <v>-1.8719</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.7105</v>
+        <v>-0.5513</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1478</v>
+        <v>-1.3206</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1</v>
+        <v>-0.2897</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5733</v>
+        <v>-0.6935</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6733</v>
+        <v>0.4039</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2538</v>
+        <v>0.1114</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8988</v>
+        <v>-0.092</v>
       </c>
       <c r="U22" t="n">
-        <v>0.645</v>
+        <v>0.2035</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5983000000000001</v>
+        <v>1.2296</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0.011</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-1.181</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.9370000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.2439</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.4886</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.4836</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.4644</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.3492</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1344</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1457</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. CRUZ URBANEJA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.3117</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.7688</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2517</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.2412</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.9579</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7163</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.2416</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.9684</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.968</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.4732</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.524</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. PALLARES ARUMI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.338</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.4381</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.1001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.4626</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.2838</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.8212</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.7105</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.1478</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.5733</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2538</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.8988</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.5983000000000001</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.5983000000000001</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484370_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.175199999999999</v>
       </c>
-      <c r="E23" t="n">
-        <v>-9.856299999999999</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E26" t="n">
+        <v>-9.856199999999999</v>
+      </c>
+      <c r="F26" t="n">
         <v>11.0317</v>
       </c>
-      <c r="G23" t="n">
-        <v>-0.3927999999999996</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-8.486899999999999</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="G26" t="n">
+        <v>-0.3928</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-8.486799999999999</v>
+      </c>
+      <c r="I26" t="n">
         <v>8.094100000000001</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J26" t="n">
         <v>0.5288999999999997</v>
       </c>
-      <c r="K23" t="n">
-        <v>-2.851300000000001</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K26" t="n">
+        <v>-2.8513</v>
+      </c>
+      <c r="L26" t="n">
         <v>3.3803</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M26" t="n">
         <v>-0.9218000000000001</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-5.6356</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>4.7137</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>1.9534</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>13.6739</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>1.7196</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-2.4334</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>4.1531</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-2.1051</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>3.7686</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-5.8736</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
